--- a/docs/go-guide.xlsx
+++ b/docs/go-guide.xlsx
@@ -1640,7 +1640,7 @@
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="3" max="3" width="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/api/duties/:id → "12" (文字列)</t>
+          <t xml:space="preserve">/api/lottery-results/:id → "12" (文字列)</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">/api/duties?status=done</t>
+          <t xml:space="preserve">/api/lottery-results?status=done</t>
         </is>
       </c>
     </row>
